--- a/diagrams/juryButtons/JuryButtons.xlsx
+++ b/diagrams/juryButtons/JuryButtons.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms-firmata\diagrams\juryButtons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F497E05C-ECA0-4E3A-9DD1-E9E790B6B47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21846A3-F6F4-4868-AB42-4EDBBEE448BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F9C8F068-60C0-4FDD-8C1E-880F519290ED}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F9C8F068-60C0-4FDD-8C1E-880F519290ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Jury" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="44">
   <si>
     <t>pin</t>
   </si>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>Resume Competition</t>
+  </si>
+  <si>
+    <t>Challenge</t>
+  </si>
+  <si>
+    <t>challenge</t>
   </si>
 </sst>
 </file>
@@ -569,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{068CC8FA-5BAB-452A-BED2-2AD75A3C9C5E}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
@@ -634,7 +640,7 @@
         <v>16</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>3</v>
@@ -719,7 +725,7 @@
         <v>41</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>3</v>
@@ -733,28 +739,27 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="5">
-        <v>12</v>
-      </c>
-      <c r="C9" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
       <c r="G9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B10" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1"/>
       <c r="G10" s="2" t="s">
@@ -764,15 +769,15 @@
         <v>36</v>
       </c>
       <c r="I10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B11" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="1"/>
       <c r="G11" s="2" t="s">
@@ -782,33 +787,33 @@
         <v>36</v>
       </c>
       <c r="I11" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="4">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="B12" s="5">
+        <v>10</v>
       </c>
       <c r="C12" s="1"/>
       <c r="G12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="I12" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4">
         <v>14</v>
-      </c>
-      <c r="B13" s="4">
-        <v>15</v>
       </c>
       <c r="C13" s="1"/>
       <c r="G13" s="2" t="s">
@@ -818,15 +823,15 @@
         <v>13</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1"/>
       <c r="G14" s="2" t="s">
@@ -836,15 +841,15 @@
         <v>13</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1"/>
       <c r="G15" s="2" t="s">
@@ -854,15 +859,15 @@
         <v>13</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" s="1"/>
       <c r="G16" s="2" t="s">
@@ -872,15 +877,15 @@
         <v>13</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1"/>
       <c r="G17" s="2" t="s">
@@ -890,6 +895,24 @@
         <v>13</v>
       </c>
       <c r="I17" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="4">
+        <v>19</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="G18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>28</v>
       </c>
     </row>
